--- a/datosSesionesPValues.xlsx
+++ b/datosSesionesPValues.xlsx
@@ -533,13 +533,13 @@
         <v>0.003122157963500858</v>
       </c>
       <c r="D2" t="n">
-        <v>0.008645917509526861</v>
+        <v>0.009152275241736774</v>
       </c>
       <c r="E2" t="n">
         <v>0.02006602777870221</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7177097159197551</v>
+        <v>0.0007181992517137232</v>
       </c>
       <c r="G2" t="n">
         <v>6.685035424757741e-07</v>
@@ -594,13 +594,13 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004819565574557498</v>
+        <v>0.004692252381909537</v>
       </c>
       <c r="E3" t="n">
         <v>0.009203052718875039</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2747020815667855</v>
+        <v>0.005449683515409399</v>
       </c>
       <c r="G3" t="n">
         <v>0.0006689294238112253</v>
@@ -649,58 +649,58 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.008645917509526861</v>
+        <v>0.009152275241736774</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004819565574557498</v>
+        <v>0.004692252381909537</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7012922357574296</v>
+        <v>0.6856520957845387</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1599796760933996</v>
+        <v>3.472437288137777e-14</v>
       </c>
       <c r="G4" t="n">
-        <v>7.373032575504601e-09</v>
+        <v>9.050759613185981e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>2.576195188617999e-07</v>
+        <v>3.164457241483916e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>1.223419916222625e-08</v>
+        <v>1.201614004519184e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>2.132820764857933e-12</v>
+        <v>3.680989371059365e-12</v>
       </c>
       <c r="K4" t="n">
-        <v>5.35651235092452e-10</v>
+        <v>8.797528666048525e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>4.183304243405237e-05</v>
+        <v>3.676561074139283e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>2.156183638918973e-05</v>
+        <v>2.212959078942322e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0004716582535115715</v>
+        <v>0.0004766341274939075</v>
       </c>
       <c r="O4" t="n">
-        <v>5.845885312506912e-06</v>
+        <v>6.154124010424508e-06</v>
       </c>
       <c r="P4" t="n">
-        <v>2.95379615834805e-22</v>
+        <v>6.967804998722322e-22</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.48400944801671e-15</v>
+        <v>7.051024950136306e-15</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02400012946543877</v>
+        <v>0.02226282478554931</v>
       </c>
       <c r="S4" t="n">
-        <v>0.006787992256488995</v>
+        <v>0.006177808359228521</v>
       </c>
     </row>
     <row r="5">
@@ -716,13 +716,13 @@
         <v>0.009203052718875039</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7012922357574296</v>
+        <v>0.6856520957845387</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2739058206207733</v>
+        <v>0.4511528835421044</v>
       </c>
       <c r="G5" t="n">
         <v>1.232665091618104e-06</v>
@@ -771,58 +771,58 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7177097159197551</v>
+        <v>0.0007181992517137232</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2747020815667855</v>
+        <v>0.005449683515409399</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1599796760933996</v>
+        <v>3.472437288137777e-14</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2739058206207733</v>
+        <v>0.4511528835421044</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4851516564914525</v>
+        <v>6.163802595845071e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7022603879657837</v>
+        <v>2.713069062853801e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1022747013916069</v>
+        <v>5.507079006774148e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9133325979797187</v>
+        <v>2.499845939867045e-11</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6673421092757914</v>
+        <v>5.812346789135855e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1060294292839936</v>
+        <v>0.004240148737054108</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2021998141508706</v>
+        <v>4.358553818723888e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2523725817875805</v>
+        <v>3.167669656123115e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>0.240541234860223</v>
+        <v>1.086385154027874e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>0.519719708090715</v>
+        <v>2.784188945252887e-17</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2443247886234537</v>
+        <v>6.426400504188234e-14</v>
       </c>
       <c r="R6" t="n">
-        <v>0.03146197727197204</v>
+        <v>0.001027046947150208</v>
       </c>
       <c r="S6" t="n">
-        <v>0.02690674471959123</v>
+        <v>0.000576156228196568</v>
       </c>
     </row>
     <row r="7">
@@ -838,13 +838,13 @@
         <v>0.0006689294238112253</v>
       </c>
       <c r="D7" t="n">
-        <v>7.373032575504601e-09</v>
+        <v>9.050759613185981e-09</v>
       </c>
       <c r="E7" t="n">
         <v>1.232665091618104e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4851516564914525</v>
+        <v>6.163802595845071e-10</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>0.0005058539788052024</v>
       </c>
       <c r="D8" t="n">
-        <v>2.576195188617999e-07</v>
+        <v>3.164457241483916e-07</v>
       </c>
       <c r="E8" t="n">
         <v>2.192489388450195e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7022603879657837</v>
+        <v>2.713069062853801e-08</v>
       </c>
       <c r="G8" t="n">
         <v>6.573595509910822e-55</v>
@@ -960,13 +960,13 @@
         <v>0.05247464264449371</v>
       </c>
       <c r="D9" t="n">
-        <v>1.223419916222625e-08</v>
+        <v>1.201614004519184e-08</v>
       </c>
       <c r="E9" t="n">
         <v>0.04026643359901672</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1022747013916069</v>
+        <v>5.507079006774148e-09</v>
       </c>
       <c r="G9" t="n">
         <v>1.808471584627107e-13</v>
@@ -1021,13 +1021,13 @@
         <v>0.000608010607022145</v>
       </c>
       <c r="D10" t="n">
-        <v>2.132820764857933e-12</v>
+        <v>3.680989371059365e-12</v>
       </c>
       <c r="E10" t="n">
         <v>7.536529139562891e-05</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9133325979797187</v>
+        <v>2.499845939867045e-11</v>
       </c>
       <c r="G10" t="n">
         <v>5.68519229194127e-33</v>
@@ -1082,13 +1082,13 @@
         <v>0.0006674855266465694</v>
       </c>
       <c r="D11" t="n">
-        <v>5.35651235092452e-10</v>
+        <v>8.797528666048525e-10</v>
       </c>
       <c r="E11" t="n">
         <v>0.0001027033376695209</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6673421092757914</v>
+        <v>5.812346789135855e-10</v>
       </c>
       <c r="G11" t="n">
         <v>1.298302868461554e-31</v>
@@ -1143,13 +1143,13 @@
         <v>0.4183617179810802</v>
       </c>
       <c r="D12" t="n">
-        <v>4.183304243405237e-05</v>
+        <v>3.676561074139283e-05</v>
       </c>
       <c r="E12" t="n">
         <v>0.2640194505634427</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1060294292839936</v>
+        <v>0.004240148737054108</v>
       </c>
       <c r="G12" t="n">
         <v>0.04773360853621536</v>
@@ -1204,13 +1204,13 @@
         <v>0.002644120521789591</v>
       </c>
       <c r="D13" t="n">
-        <v>2.156183638918973e-05</v>
+        <v>2.212959078942322e-05</v>
       </c>
       <c r="E13" t="n">
         <v>5.623122067396673e-07</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2021998141508706</v>
+        <v>4.358553818723888e-07</v>
       </c>
       <c r="G13" t="n">
         <v>3.974932710229319e-40</v>
@@ -1265,13 +1265,13 @@
         <v>0.00216041688861026</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0004716582535115715</v>
+        <v>0.0004766341274939075</v>
       </c>
       <c r="E14" t="n">
         <v>8.154692699404531e-09</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2523725817875805</v>
+        <v>3.167669656123115e-05</v>
       </c>
       <c r="G14" t="n">
         <v>1.174178725091201e-30</v>
@@ -1326,13 +1326,13 @@
         <v>0.05783124841926914</v>
       </c>
       <c r="D15" t="n">
-        <v>5.845885312506912e-06</v>
+        <v>6.154124010424508e-06</v>
       </c>
       <c r="E15" t="n">
         <v>0.05958083762163353</v>
       </c>
       <c r="F15" t="n">
-        <v>0.240541234860223</v>
+        <v>1.086385154027874e-07</v>
       </c>
       <c r="G15" t="n">
         <v>1.846440525867538e-14</v>
@@ -1387,13 +1387,13 @@
         <v>0.000251970447006775</v>
       </c>
       <c r="D16" t="n">
-        <v>2.95379615834805e-22</v>
+        <v>6.967804998722322e-22</v>
       </c>
       <c r="E16" t="n">
         <v>0.004897872537584374</v>
       </c>
       <c r="F16" t="n">
-        <v>0.519719708090715</v>
+        <v>2.784188945252887e-17</v>
       </c>
       <c r="G16" t="n">
         <v>5.322745397533213e-20</v>
@@ -1448,13 +1448,13 @@
         <v>0.0007758086201941599</v>
       </c>
       <c r="D17" t="n">
-        <v>5.48400944801671e-15</v>
+        <v>7.051024950136306e-15</v>
       </c>
       <c r="E17" t="n">
         <v>0.0007429950113155776</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2443247886234537</v>
+        <v>6.426400504188234e-14</v>
       </c>
       <c r="G17" t="n">
         <v>1.268653755703755e-21</v>
@@ -1509,13 +1509,13 @@
         <v>0.03652377106852549</v>
       </c>
       <c r="D18" t="n">
-        <v>0.02400012946543877</v>
+        <v>0.02226282478554931</v>
       </c>
       <c r="E18" t="n">
         <v>0.0556947885098445</v>
       </c>
       <c r="F18" t="n">
-        <v>0.03146197727197204</v>
+        <v>0.001027046947150208</v>
       </c>
       <c r="G18" t="n">
         <v>0.6060985258137933</v>
@@ -1570,13 +1570,13 @@
         <v>0.02535588356884267</v>
       </c>
       <c r="D19" t="n">
-        <v>0.006787992256488995</v>
+        <v>0.006177808359228521</v>
       </c>
       <c r="E19" t="n">
         <v>0.2348797714137206</v>
       </c>
       <c r="F19" t="n">
-        <v>0.02690674471959123</v>
+        <v>0.000576156228196568</v>
       </c>
       <c r="G19" t="n">
         <v>0.9197086297798601</v>
